--- a/artfynd/A 24036-2025 artfynd.xlsx
+++ b/artfynd/A 24036-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>85917926</v>
+        <v>86354505</v>
       </c>
       <c r="B2" t="n">
-        <v>55392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>56884</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208257</v>
+        <v>208255</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -718,22 +713,30 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dalen, Sotenäs kommun, Götaland, Rished, Västra Götalands län, Boh</t>
+          <t>Soldattorpet Håle Dalar, Soldattorpet Håle Dalar, Sotenäs, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>286389.6958355612</v>
+        <v>286025</v>
       </c>
       <c r="R2" t="n">
-        <v>6477620.53638129</v>
+        <v>6477184</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,22 +760,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-05-31</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:38</t>
+          <t>2020-06-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-05-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:38</t>
+          <t>2020-06-19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,6 +789,125 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>85917926</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56876</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>208257</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kopparödla</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Anguis fragilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Dalen, Sotenäs kommun, Götaland, Rished, Västra Götalands län, Boh</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>286390</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6477621</v>
+      </c>
+      <c r="S3" t="n">
+        <v>8</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sotenäs</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Askum</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2020-05-31</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2020-05-31</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Kristian Kjellberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Kristian Kjellberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24036-2025 artfynd.xlsx
+++ b/artfynd/A 24036-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86354505</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,8 +918,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85917926</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>